--- a/static/data/database/JSS2_Students.xlsx
+++ b/static/data/database/JSS2_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JSS2 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS2 Students'!$A$1:$H$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS2 Students'!$A$1:$H$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,12 +473,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std071</t>
+          <t>std001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Muritala</t>
+          <t>Abdulhakeem</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,14 +486,10 @@
           <t>Maryam</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>O.</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0706578164?</t>
+          <t>08036544???</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,32 +511,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std072</t>
+          <t>std007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Azeema</t>
+          <t>Hafeez</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>Harith</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08028038331</t>
+          <t>08027283163</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,32 +553,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std073</t>
+          <t>std013</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abdulazeez</t>
+          <t>Abdulaziz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fatima</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Zahra</t>
-        </is>
-      </c>
+          <t>Kura</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08033955669</t>
+          <t>08065353705</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -599,27 +591,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std074</t>
+          <t>std015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rukayya</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>M.</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08161780806</t>
+          <t>0806517?03?</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -641,27 +633,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std075</t>
+          <t>std023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Isah</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rehmat</t>
+          <t>Muklisah</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Adepeju</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08166839781</t>
+          <t>08032190197</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -671,7 +663,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -683,27 +675,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std076</t>
+          <t>std024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zaiyanu</t>
+          <t>Abbakura</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Firdausi</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>Sadiq</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08030727742</t>
+          <t>08032109398</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -713,7 +705,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -725,23 +717,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std077</t>
+          <t>std027</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Abbakura</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Helima</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Zaynab</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08034132061</t>
+          <t>08032109398</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -751,7 +747,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -763,27 +759,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std078</t>
+          <t>std030</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aliyu</t>
+          <t>Audu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Shafii</t>
-        </is>
-      </c>
+          <t>Fadilah</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>07073306335</t>
+          <t>08033738117</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -793,7 +785,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -805,37 +797,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std079</t>
+          <t>std035</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Summayya</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Sani</t>
-        </is>
-      </c>
+          <t>Ibrahim</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08036583992</t>
+          <t>08035839220</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -847,33 +835,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std080</t>
+          <t>std037</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salisu</t>
+          <t>Abdulhakeem</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Al-amin</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08035704468</t>
+          <t>08062518827</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -885,23 +877,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std081</t>
+          <t>std040</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abdulkarim</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amir</t>
+          <t>Muaz</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08066569810</t>
+          <t>08036964091</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -911,7 +903,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -923,37 +915,33 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std082</t>
+          <t>std047</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ibeleye</t>
+          <t>Abdulrahman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mercy</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>O.</t>
-        </is>
-      </c>
+          <t>Auwal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>07033281815</t>
+          <t>08033973137</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -965,33 +953,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std083</t>
+          <t>std048</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abdulmalik</t>
+          <t>Abdulrahim</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Marufat</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08036475917</t>
+          <t>08032865130</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1003,37 +991,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std084</t>
+          <t>std049</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Khadijah</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
+          <t>Abdulrahman</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08066009732</t>
+          <t>08062732619</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1045,37 +1029,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std085</t>
+          <t>std050</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abdulquadir</t>
+          <t>Abdulmalik</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muneerah</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>Ubandoma</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08061156643</t>
+          <t>07068718854</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1087,23 +1071,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std086</t>
+          <t>std052</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Otun</t>
+          <t>Anointed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kamaldeen</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Onoja</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08033806730</t>
+          <t>08067028585</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1113,7 +1101,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1125,33 +1113,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std087</t>
+          <t>std053</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Momah</t>
+          <t>Akinloye</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mukhiis</t>
+          <t>Goodness</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07065477281</t>
+          <t>08058010495</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1163,23 +1151,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std088</t>
+          <t>std054</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Musa</t>
+          <t>Amar</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Nimlan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08073754???</t>
+          <t>09060778131</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1189,7 +1177,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1201,37 +1189,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std089</t>
+          <t>std055</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Abba</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Mamman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Anif</t>
+          <t>Ummahani</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>07068111313</t>
+          <t>08031357581</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1243,23 +1231,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std090</t>
+          <t>std064</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Abdul-Basit</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Adamu</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sambo</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0703209857?</t>
+          <t>07065914224</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1269,7 +1261,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1281,28 +1273,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std091</t>
+          <t>std071</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Suleiman</t>
+          <t>Muritala</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Abdurshman</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>O.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07036735553</t>
+          <t>0706578164?</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1319,32 +1315,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std092</t>
+          <t>std072</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Saliuh</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Abba</t>
+          <t>Azeema</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08033326027</t>
+          <t>08028038331</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1361,28 +1357,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std093</t>
+          <t>std073</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Uruwatu</t>
+          <t>Abdulazeez</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Gawal</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zahra</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08067276386</t>
+          <t>08033955669</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1399,28 +1399,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std094</t>
+          <t>std074</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Yahaya</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Rukayya</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>M.</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08031570962</t>
+          <t>08161780806</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1437,27 +1441,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std095</t>
+          <t>std075</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Saeed</t>
+          <t>Isah</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mufidah</t>
+          <t>Rehmat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rabi</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>07031650002</t>
+          <t>08166839781</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1479,23 +1483,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std096</t>
+          <t>std076</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Balkis</t>
+          <t>Zaiyanu</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ashiru</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Firdausi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08032444824</t>
+          <t>08030727742</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1517,23 +1525,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std097</t>
+          <t>std077</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Zaafirah</t>
+          <t>Helima</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>07081364056</t>
+          <t>08034132061</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1543,7 +1551,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1555,27 +1563,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std098</t>
+          <t>std078</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nabi</t>
+          <t>Aliyu</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Zainab</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Shafii</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08065444560</t>
+          <t>07073306335</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1585,7 +1593,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1597,27 +1605,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std099</t>
+          <t>std079</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hibbatullah</t>
+          <t>Summayya</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(Yaseery)</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08072492429</t>
+          <t>08036583992</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1639,33 +1647,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std100</t>
+          <t>std080</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Salisu</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Abdul</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08037757400</t>
+          <t>08035704468</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1677,37 +1685,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std101</t>
+          <t>std081</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Abdulkarim</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Husna</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
+          <t>Amir</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0803414215?</t>
+          <t>08066569810</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1719,33 +1723,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std102</t>
+          <t>std082</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Umar</t>
+          <t>Ibeleye</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Abdulkareem</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>Mercy</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>O.</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08094266649</t>
+          <t>07033281815</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1757,37 +1765,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std103</t>
+          <t>std083</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abdulmalik</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jamil</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Hussaini</t>
-        </is>
-      </c>
+          <t>Marufat</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08156774462</t>
+          <t>08036475917</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1799,33 +1803,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std104</t>
+          <t>std084</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Abdulrahzaq</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Olaide</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Khadijah</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08029755760</t>
+          <t>08066009732</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1837,27 +1845,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std105</t>
+          <t>std085</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Adab</t>
+          <t>Abdulquadir</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Muneerah</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Benjatte</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08032038321</t>
+          <t>08061156643</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1867,7 +1875,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1879,37 +1887,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std106</t>
+          <t>std086</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Malam</t>
+          <t>Otun</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fatima</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Sadiqee</t>
-        </is>
-      </c>
+          <t>Kamaldeen</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08036447082</t>
+          <t>08033806730</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1921,27 +1925,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std107</t>
+          <t>std087</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Momah</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mubarak</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>A.</t>
-        </is>
-      </c>
+          <t>Mukhiis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08057749026</t>
+          <t>07065477281</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1963,27 +1963,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std108</t>
+          <t>std088</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Musa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sadiq</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Ibrahim</t>
-        </is>
-      </c>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08036584041</t>
+          <t>08073754???</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1993,7 +1989,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2005,37 +2001,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std109</t>
+          <t>std089</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shuaibu</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Aytu</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Khadijah Mathini</t>
+          <t>Anif</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08161777190</t>
+          <t>07068111313</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2047,33 +2043,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std110</t>
+          <t>std090</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bashir</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Abdul-Basit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08032183102</t>
+          <t>0703209857?</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2085,37 +2081,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std111</t>
+          <t>std091</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aliyu</t>
+          <t>Suleiman</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Khadija</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Abdul Bilil</t>
-        </is>
-      </c>
+          <t>Abdurshman</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08060523051</t>
+          <t>07036735553</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2127,37 +2119,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std112</t>
+          <t>std092</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Muritala</t>
+          <t>Saliuh</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rufaina</t>
+          <t>Abba</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>07065564454</t>
+          <t>08033326027</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2169,33 +2161,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std113</t>
+          <t>std093</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
+          <t>Uruwatu</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Khadija</t>
+          <t>Gawal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>07037738374</t>
+          <t>08067276386</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2207,37 +2199,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std114</t>
+          <t>std094</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Aminu</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fatima</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Jibo</t>
-        </is>
-      </c>
+          <t>Yahaya</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08077723757</t>
+          <t>08031570962</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2249,27 +2237,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std115</t>
+          <t>std095</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Musa</t>
+          <t>Saeed</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shehu</t>
+          <t>Mufidah</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Rabi</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>07034098967</t>
+          <t>07031650002</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2279,7 +2267,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2291,37 +2279,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std116</t>
+          <t>std096</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Balkis</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Francisca</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
+          <t>Ashiru</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>07018362448</t>
+          <t>08032444824</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2333,32 +2317,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std117</t>
+          <t>std097</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Munir</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Kabir</t>
-        </is>
-      </c>
+          <t>Zaafirah</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08036795373</t>
+          <t>07081364056</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2375,28 +2355,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std118</t>
+          <t>std098</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sa'ad</t>
+          <t>Nabi</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Abdulsalam</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Maryam</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08025512088</t>
+          <t>08065444560</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2413,32 +2397,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std119</t>
+          <t>std099</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Mohammed</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>Hibbatullah</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Haruna</t>
+          <t>(Yaseery)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08035887544</t>
+          <t>08072492429</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2455,27 +2439,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std120</t>
+          <t>std100</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Shareef</t>
-        </is>
-      </c>
+          <t>Abdul</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08035878237</t>
+          <t>08037757400</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2497,32 +2477,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>std121</t>
+          <t>std101</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Olarinde</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>Husna</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Olamitumide</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0803223285?</t>
+          <t>0803414215?</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2539,28 +2519,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>std122</t>
+          <t>std102</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Umar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Maimuna</t>
+          <t>Abdulkareem</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>08028573220</t>
+          <t>08094266649</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2577,32 +2557,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>std123</t>
+          <t>std103</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Salau</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Isayo</t>
+          <t>Jamil</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Khalifa</t>
+          <t>Hussaini</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08035096471</t>
+          <t>08156774462</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2619,27 +2599,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>std124</t>
+          <t>std104</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Abdulrahzaq</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Luqman</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Hanafi</t>
-        </is>
-      </c>
+          <t>Olaide</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>07033162971</t>
+          <t>08029755760</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2661,23 +2637,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>std125</t>
+          <t>std105</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Adab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ismat</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Benjatte</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08032892838</t>
+          <t>08032038321</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2699,23 +2679,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>std126</t>
+          <t>std106</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Malam</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nabeela</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sadiqee</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08009997778</t>
+          <t>08036447082</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2737,27 +2721,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>std127</t>
+          <t>std107</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rabiu</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Mubarak</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Al-Mustapha</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>07032297722</t>
+          <t>08057749026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2779,23 +2763,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>std128</t>
+          <t>std108</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Alhassan</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ashiru</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Sadiq</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ibrahim</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08165650509</t>
+          <t>08036584041</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2817,27 +2805,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std129</t>
+          <t>std109</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yakubu</t>
+          <t>Shuaibu</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nabeela</t>
+          <t>Aytu</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Limar</t>
+          <t>Khadijah Mathini</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08163234854</t>
+          <t>08161777190</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2847,7 +2835,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2859,37 +2847,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std130</t>
+          <t>std110</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Bashir</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Yusuf</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Sani</t>
-        </is>
-      </c>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08032894993</t>
+          <t>08032183102</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2901,27 +2885,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std131</t>
+          <t>std111</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Aliyu</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rahma</t>
+          <t>Khadija</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Abdul Bilil</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08033752523</t>
+          <t>08060523051</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2931,7 +2915,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2943,37 +2927,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std132</t>
+          <t>std112</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Abdulganiyu</t>
+          <t>Muritala</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Muritala</t>
+          <t>Rufaina</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>D.</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08031526007</t>
+          <t>07065564454</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2985,27 +2969,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std133</t>
+          <t>std113</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Balarabe</t>
+          <t>Abdulrahman</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Yusuf</t>
-        </is>
-      </c>
+          <t>Khadija</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>07044322222</t>
+          <t>07037738374</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3015,7 +2995,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3027,37 +3007,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std134</t>
+          <t>std114</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Aminu</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Omolori</t>
+          <t>Jibo</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08033821780</t>
+          <t>08077723757</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3069,23 +3049,27 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std135</t>
+          <t>std115</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lukman</t>
+          <t>Musa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Shehu</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08133393282</t>
+          <t>07034098967</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3095,7 +3079,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3107,37 +3091,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std136</t>
+          <t>std116</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rabiu</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Francisca</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Alhassan</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>07030453600</t>
+          <t>07018362448</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3149,23 +3133,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std137</t>
+          <t>std117</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hussein</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mukhtar</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Munir</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>07035352050</t>
+          <t>08036795373</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3175,7 +3163,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3187,37 +3175,33 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std138</t>
+          <t>std118</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Sa'ad</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Imran</t>
-        </is>
-      </c>
+          <t>Abdulsalam</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08033166893</t>
+          <t>08025512088</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3229,27 +3213,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std139</t>
+          <t>std119</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ilyasu</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Mu'id</t>
+          <t>Haruna</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08062198188</t>
+          <t>08035887544</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3259,7 +3243,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3271,37 +3255,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std140</t>
+          <t>std120</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Usman</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hafsat</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Mari</t>
+          <t>Shareef</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08026033049</t>
+          <t>08035878237</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3313,27 +3297,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std141</t>
+          <t>std121</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Olarinde</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sabo</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Olamitumide</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08036880438</t>
+          <t>0803223285?</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3343,7 +3327,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3355,23 +3339,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std142</t>
+          <t>std122</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Maimuna</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>080358681604?</t>
+          <t>08028573220</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3381,7 +3365,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3393,33 +3377,37 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std143</t>
+          <t>std123</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Salau</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Haliru</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Isayo</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Khalifa</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08032332868</t>
+          <t>08035096471</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3431,37 +3419,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std144</t>
+          <t>std124</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Ibrahim</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Farida</t>
+          <t>Luqman</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Sadiq</t>
+          <t>Hanafi</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>07035983882</t>
+          <t>07033162971</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3473,37 +3461,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>std145</t>
+          <t>std125</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Haliru</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sadiq</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Akubursa</t>
-        </is>
-      </c>
+          <t>Ismat</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08060671508</t>
+          <t>08032892838</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3515,27 +3499,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>std146</t>
+          <t>std126</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bawa</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bilikisu</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Abubakar</t>
-        </is>
-      </c>
+          <t>Nabeela</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>08065554954</t>
+          <t>08009997778</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3545,7 +3525,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3557,23 +3537,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>std147</t>
+          <t>std127</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rabiu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Idris</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Al-Mustapha</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>08123584340</t>
+          <t>07032297722</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3583,7 +3567,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3595,33 +3579,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>std148</t>
+          <t>std128</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Alhassan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Ashiru</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>08100999778</t>
+          <t>08165650509</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3633,27 +3617,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>std149</t>
+          <t>std129</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Abdallah</t>
+          <t>Yakubu</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hasina</t>
+          <t>Nabeela</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Limar</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>08034423215</t>
+          <t>08163234854</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3675,32 +3659,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>std150</t>
+          <t>std130</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Wonukai</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>08065359057</t>
+          <t>08032894993</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3717,27 +3701,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>std151</t>
+          <t>std131</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Halima</t>
+          <t>Rahma</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Arfo</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08069661006</t>
+          <t>08033752523</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3759,32 +3743,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>std152</t>
+          <t>std132</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Rabiu</t>
+          <t>Abdulganiyu</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Muritala</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ojali</t>
+          <t>D.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>07031591970</t>
+          <t>08031526007</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3801,27 +3785,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>std153</t>
+          <t>std133</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Babagida</t>
+          <t>Balarabe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>07032901805</t>
+          <t>07044322222</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3843,28 +3827,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>std154</t>
+          <t>std134</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bashir</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hanifa</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Sani</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Omolori</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>08069205599</t>
+          <t>08033821780</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3881,28 +3869,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>std155</t>
+          <t>std135</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Abdulladir</t>
+          <t>Lukman</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mushibahu</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08065895999</t>
+          <t>08133393282</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3919,27 +3907,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>std156</t>
+          <t>std136</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aminu</t>
+          <t>Rabiu</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Dahiru</t>
+          <t>Alhassan</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>080377885??</t>
+          <t>07030453600</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3961,24 +3949,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>std157</t>
+          <t>std137</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ishaq</t>
+          <t>Hussein</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Aliyu</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Lolo</t>
-        </is>
-      </c>
+          <t>Mukhtar</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>07035352050</t>
@@ -4003,32 +3987,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>std158</t>
+          <t>std138</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Onuche</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Imran</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08067871919</t>
+          <t>08033166893</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4045,47 +4029,863 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>std139</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ilyasu</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mu'id</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>08062198188</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>std140</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Usman</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Hafsat</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Mari</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>08026033049</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>std141</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sabo</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>08036880438</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>std142</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>080358681604?</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>std143</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Haliru</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>08032332868</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>std144</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Abubakar</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Farida</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sadiq</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>07035983882</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>std145</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Haliru</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sadiq</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Akubursa</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>08060671508</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>std146</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Bawa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bilikisu</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Abubakar</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>08065554954</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>std147</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>08123584340</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>std148</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Idris</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>08100999778</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>std149</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Abdallah</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Hasina</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>08034423215</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>std150</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Abdullahi</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wonukai</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>08065359057</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>std151</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Mustapha</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Halima</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Arfo</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>08069661006</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>std152</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Rabiu</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Jasmine</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Ojali</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>07031591970</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>std153</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Babagida</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>07032901805</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>std154</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Bashir</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Hanifa</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>08069205599</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>std155</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Abdulladir</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Mushibahu</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>08065895999</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>std156</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Aminu</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Dahiru</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>080377885??</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>std157</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ishaq</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Aliyu</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lolo</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>07035352050</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>std158</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Mustapha</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Onuche</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>08067871919</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>JSS2C</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>JSS2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>std159</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Ashiru</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>Al-Hussein</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>I.</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>08165650569</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>JSS2C</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>JSS2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H90"/>
+  <autoFilter ref="A1:H110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/static/data/database/JSS2_Students.xlsx
+++ b/static/data/database/JSS2_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JSS2 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS2 Students'!$A$1:$H$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'JSS2 Students'!$A$1:$H$90</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,12 +473,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std001</t>
+          <t>std071</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Abdulhakeem</t>
+          <t>Muritala</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,10 +486,14 @@
           <t>Maryam</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>O.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08036544???</t>
+          <t>0706578164?</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,32 +515,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std007</t>
+          <t>std072</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hafeez</t>
+          <t>Azeema</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Harith</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08027283163</t>
+          <t>08028038331</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -553,28 +557,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std013</t>
+          <t>std073</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Abdulaziz</t>
+          <t>Abdulazeez</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kura</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Zahra</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08065353705</t>
+          <t>08033955669</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -591,27 +599,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std015</t>
+          <t>std074</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Rukayya</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>M.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0806517?03?</t>
+          <t>08161780806</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -633,27 +641,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std023</t>
+          <t>std075</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Isah</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Muklisah</t>
+          <t>Rehmat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Adepeju</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08032190197</t>
+          <t>08166839781</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -663,7 +671,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -675,27 +683,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std024</t>
+          <t>std076</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abbakura</t>
+          <t>Zaiyanu</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Firdausi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sadiq</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08032109398</t>
+          <t>08030727742</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -705,7 +713,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -717,27 +725,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std027</t>
+          <t>std077</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Abbakura</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ali</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Zaynab</t>
-        </is>
-      </c>
+          <t>Helima</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08032109398</t>
+          <t>08034132061</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -747,7 +751,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -759,23 +763,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std030</t>
+          <t>std078</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audu</t>
+          <t>Aliyu</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fadilah</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Zainab</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Shafii</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08033738117</t>
+          <t>07073306335</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -785,7 +793,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -797,33 +805,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std035</t>
+          <t>std079</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Summayya</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sani</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08035839220</t>
+          <t>08036583992</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -835,37 +847,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std037</t>
+          <t>std080</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Abdulhakeem</t>
+          <t>Salisu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Al-amin</t>
-        </is>
-      </c>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08062518827</t>
+          <t>08035704468</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -877,23 +885,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std040</t>
+          <t>std081</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Abdulkarim</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Muaz</t>
+          <t>Amir</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08036964091</t>
+          <t>08066569810</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -903,7 +911,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -915,33 +923,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std047</t>
+          <t>std082</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
+          <t>Ibeleye</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auwal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Mercy</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>O.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08033973137</t>
+          <t>07033281815</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -953,33 +965,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std048</t>
+          <t>std083</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Abdulrahim</t>
+          <t>Abdulmalik</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>Marufat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08032865130</t>
+          <t>08036475917</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -991,33 +1003,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std049</t>
+          <t>std084</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Khadijah</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08062732619</t>
+          <t>08066009732</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1029,37 +1045,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std050</t>
+          <t>std085</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abdulmalik</t>
+          <t>Abdulquadir</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Muneerah</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ubandoma</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>07068718854</t>
+          <t>08061156643</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1071,27 +1087,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std052</t>
+          <t>std086</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Anointed</t>
+          <t>Otun</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Peter</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Onoja</t>
-        </is>
-      </c>
+          <t>Kamaldeen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08067028585</t>
+          <t>08033806730</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1101,7 +1113,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1113,33 +1125,33 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std053</t>
+          <t>std087</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Akinloye</t>
+          <t>Momah</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Goodness</t>
+          <t>Mukhiis</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08058010495</t>
+          <t>07065477281</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1151,23 +1163,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std054</t>
+          <t>std088</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Amar</t>
+          <t>Musa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nimlan</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>09060778131</t>
+          <t>08073754???</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1177,7 +1189,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1189,37 +1201,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std055</t>
+          <t>std089</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abba</t>
+          <t>Yusuf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mamman</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ummahani</t>
+          <t>Anif</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08031357581</t>
+          <t>07068111313</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1231,27 +1243,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std064</t>
+          <t>std090</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Isa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Adamu</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Sambo</t>
-        </is>
-      </c>
+          <t>Abdul-Basit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>07065914224</t>
+          <t>0703209857?</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1261,7 +1269,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>JSS2C</t>
+          <t>JSS2A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1273,32 +1281,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std071</t>
+          <t>std091</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Muritala</t>
+          <t>Suleiman</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>O.</t>
-        </is>
-      </c>
+          <t>Abdurshman</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0706578164?</t>
+          <t>07036735553</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1315,32 +1319,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std072</t>
+          <t>std092</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Saliuh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Abba</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>Mustapha</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Azeema</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>O.</t>
-        </is>
-      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08028038331</t>
+          <t>08033326027</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1357,32 +1361,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std073</t>
+          <t>std093</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Abdulazeez</t>
+          <t>Uruwatu</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fatima</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Zahra</t>
-        </is>
-      </c>
+          <t>Gawal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08033955669</t>
+          <t>08067276386</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1399,32 +1399,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std074</t>
+          <t>std094</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rukayya</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>M.</t>
-        </is>
-      </c>
+          <t>Yahaya</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08161780806</t>
+          <t>08031570962</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1441,27 +1437,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std075</t>
+          <t>std095</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Isah</t>
+          <t>Saeed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rehmat</t>
+          <t>Mufidah</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Rabi</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08166839781</t>
+          <t>07031650002</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1483,27 +1479,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std076</t>
+          <t>std096</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zaiyanu</t>
+          <t>Balkis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Firdausi</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>A.</t>
-        </is>
-      </c>
+          <t>Ashiru</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08030727742</t>
+          <t>08032444824</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1525,23 +1517,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std077</t>
+          <t>std097</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Abdullah</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Helima</t>
+          <t>Zaafirah</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08034132061</t>
+          <t>07081364056</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1551,7 +1543,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1563,27 +1555,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std078</t>
+          <t>std098</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Aliyu</t>
+          <t>Nabi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zainab</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shafii</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07073306335</t>
+          <t>08065444560</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1593,7 +1585,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1605,27 +1597,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std079</t>
+          <t>std099</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mohammed</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Summayya</t>
+          <t>Hibbatullah</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>(Yaseery)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>08036583992</t>
+          <t>08072492429</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1635,7 +1627,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1647,33 +1639,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std080</t>
+          <t>std100</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Salisu</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Abdul</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08035704468</t>
+          <t>08037757400</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1685,33 +1677,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std081</t>
+          <t>std101</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abdulkarim</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Amir</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Husna</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08066569810</t>
+          <t>0803414215?</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1723,37 +1719,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std082</t>
+          <t>std102</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ibeleye</t>
+          <t>Umar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mercy</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>O.</t>
-        </is>
-      </c>
+          <t>Abdulkareem</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>07033281815</t>
+          <t>08094266649</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1765,33 +1757,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std083</t>
+          <t>std103</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abdulmalik</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marufat</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Jamil</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Hussaini</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08036475917</t>
+          <t>08156774462</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1803,37 +1799,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std084</t>
+          <t>std104</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Abdulrahzaq</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Khadijah</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Menu</t>
-        </is>
-      </c>
+          <t>Olaide</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08066009732</t>
+          <t>08029755760</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1845,27 +1837,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std085</t>
+          <t>std105</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abdulquadir</t>
+          <t>Adab</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Muneerah</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>Benjatte</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08061156643</t>
+          <t>08032038321</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1875,7 +1867,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1887,33 +1879,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std086</t>
+          <t>std106</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Otun</t>
+          <t>Malam</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kamaldeen</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sadiqee</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08033806730</t>
+          <t>08036447082</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1925,23 +1921,27 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std087</t>
+          <t>std107</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Momah</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mukhiis</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Mubarak</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>07065477281</t>
+          <t>08057749026</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1963,23 +1963,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std088</t>
+          <t>std108</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Musa</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Sadiq</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Ibrahim</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08073754???</t>
+          <t>08036584041</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1989,7 +1993,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2001,37 +2005,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std089</t>
+          <t>std109</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Shuaibu</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Aytu</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Anif</t>
+          <t>Khadijah Mathini</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>07068111313</t>
+          <t>08161777190</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2043,33 +2047,33 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std090</t>
+          <t>std110</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Isa</t>
+          <t>Bashir</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Abdul-Basit</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0703209857?</t>
+          <t>08032183102</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2081,33 +2085,37 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std091</t>
+          <t>std111</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suleiman</t>
+          <t>Aliyu</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Abdurshman</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Khadija</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Abdul Bilil</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>07036735553</t>
+          <t>08060523051</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2119,37 +2127,37 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std092</t>
+          <t>std112</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Saliuh</t>
+          <t>Muritala</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Abba</t>
+          <t>Rufaina</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mustapha</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08033326027</t>
+          <t>07065564454</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2161,33 +2169,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std093</t>
+          <t>std113</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Uruwatu</t>
+          <t>Abdulrahman</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gawal</t>
+          <t>Khadija</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08067276386</t>
+          <t>07037738374</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2199,33 +2207,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std094</t>
+          <t>std114</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Aminu</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yahaya</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Jibo</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08031570962</t>
+          <t>08077723757</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2237,27 +2249,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std095</t>
+          <t>std115</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Saeed</t>
+          <t>Musa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mufidah</t>
+          <t>Shehu</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Rabi</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>07031650002</t>
+          <t>07034098967</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2267,7 +2279,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2279,33 +2291,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std096</t>
+          <t>std116</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Balkis</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ashiru</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Francisca</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08032444824</t>
+          <t>07018362448</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>JSS2A</t>
+          <t>JSS2B</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2317,28 +2333,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std097</t>
+          <t>std117</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Abdullah</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Zaafirah</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Munir</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>07081364056</t>
+          <t>08036795373</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2355,32 +2375,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std098</t>
+          <t>std118</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nabi</t>
+          <t>Sa'ad</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Maryam</t>
-        </is>
-      </c>
+          <t>Abdulsalam</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08065444560</t>
+          <t>08025512088</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2397,32 +2413,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std099</t>
+          <t>std119</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mohammed</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hibbatullah</t>
+          <t>O.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>(Yaseery)</t>
+          <t>Haruna</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08072492429</t>
+          <t>08035887544</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2439,23 +2455,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std100</t>
+          <t>std120</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Adeyemi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Abdul</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Muhammad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Shareef</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08037757400</t>
+          <t>08035878237</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2477,32 +2497,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>std101</t>
+          <t>std121</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Olarinde</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Husna</t>
+          <t>Saad</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Olamitumide</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0803414215?</t>
+          <t>0803223285?</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2519,28 +2539,28 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>std102</t>
+          <t>std122</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Umar</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Abdulkareem</t>
+          <t>Maimuna</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>08094266649</t>
+          <t>08028573220</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2557,32 +2577,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>std103</t>
+          <t>std123</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Salau</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jamil</t>
+          <t>Isayo</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Hussaini</t>
+          <t>Khalifa</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08156774462</t>
+          <t>08035096471</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2599,23 +2619,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>std104</t>
+          <t>std124</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Abdulrahzaq</t>
+          <t>Ibrahim</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Olaide</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Luqman</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hanafi</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08029755760</t>
+          <t>07033162971</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2637,27 +2661,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>std105</t>
+          <t>std125</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Adab</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Benjatte</t>
-        </is>
-      </c>
+          <t>Ismat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08032038321</t>
+          <t>08032892838</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2679,27 +2699,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>std106</t>
+          <t>std126</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Malam</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fatima</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Sadiqee</t>
-        </is>
-      </c>
+          <t>Nabeela</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08036447082</t>
+          <t>08009997778</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2721,27 +2737,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>std107</t>
+          <t>std127</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Rabiu</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mubarak</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>Al-Mustapha</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>08057749026</t>
+          <t>07032297722</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2763,27 +2779,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>std108</t>
+          <t>std128</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Alhassan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sadiq</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Ibrahim</t>
-        </is>
-      </c>
+          <t>Ashiru</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08036584041</t>
+          <t>08165650509</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2805,27 +2817,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std109</t>
+          <t>std129</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shuaibu</t>
+          <t>Yakubu</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aytu</t>
+          <t>Nabeela</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Khadijah Mathini</t>
+          <t>Limar</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08161777190</t>
+          <t>08163234854</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2835,7 +2847,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2847,33 +2859,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std110</t>
+          <t>std130</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bashir</t>
+          <t>Abbas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fatima</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Yusuf</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sani</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08032183102</t>
+          <t>08032894993</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2885,27 +2901,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std111</t>
+          <t>std131</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aliyu</t>
+          <t>Danjuma</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Khadija</t>
+          <t>Rahma</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Abdul Bilil</t>
+          <t>Ene</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08060523051</t>
+          <t>08033752523</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2915,7 +2931,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2927,37 +2943,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std112</t>
+          <t>std132</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
+          <t>Abdulganiyu</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
           <t>Muritala</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Rufaina</t>
-        </is>
-      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>D.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>07065564454</t>
+          <t>08031526007</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2969,23 +2985,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std113</t>
+          <t>std133</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Abdulrahman</t>
+          <t>Balarabe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Khadija</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Yusuf</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>07037738374</t>
+          <t>07044322222</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2995,7 +3015,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3007,37 +3027,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std114</t>
+          <t>std134</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Aminu</t>
+          <t>Hamza</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Sani</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Jibo</t>
+          <t>Omolori</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08077723757</t>
+          <t>08033821780</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3049,27 +3069,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std115</t>
+          <t>std135</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Musa</t>
+          <t>Lukman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shehu</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Fatima</t>
-        </is>
-      </c>
+          <t>Maryam</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>07034098967</t>
+          <t>08133393282</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3079,7 +3095,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3091,37 +3107,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std116</t>
+          <t>std136</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Rabiu</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Francisca</t>
+          <t>Aisha</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bello</t>
+          <t>Alhassan</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>07018362448</t>
+          <t>07030453600</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3133,27 +3149,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std117</t>
+          <t>std137</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Hussein</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Munir</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Kabir</t>
-        </is>
-      </c>
+          <t>Mukhtar</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08036795373</t>
+          <t>07035352050</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3163,7 +3175,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3175,33 +3187,37 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std118</t>
+          <t>std138</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sa'ad</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Abdulsalam</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Imran</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08025512088</t>
+          <t>08033166893</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3213,27 +3229,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std119</t>
+          <t>std139</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Abdullahi</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>O.</t>
+          <t>Ilyasu</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Haruna</t>
+          <t>Mu'id</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08035887544</t>
+          <t>08062198188</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3243,7 +3259,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3255,37 +3271,37 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std120</t>
+          <t>std140</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adeyemi</t>
+          <t>Usman</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Hafsat</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Shareef</t>
+          <t>Mari</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08035878237</t>
+          <t>08026033049</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3297,27 +3313,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std121</t>
+          <t>std141</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Olarinde</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Saad</t>
+          <t>Sabo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Olamitumide</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0803223285?</t>
+          <t>08036880438</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3327,7 +3343,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3339,23 +3355,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std122</t>
+          <t>std142</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Maimuna</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08028573220</t>
+          <t>080358681604?</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3365,7 +3381,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3377,37 +3393,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std123</t>
+          <t>std143</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Salau</t>
+          <t>Muhammad</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Isayo</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Khalifa</t>
-        </is>
-      </c>
+          <t>Haliru</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08035096471</t>
+          <t>08032332868</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3419,37 +3431,37 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std124</t>
+          <t>std144</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ibrahim</t>
+          <t>Abubakar</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Luqman</t>
+          <t>Farida</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Hanafi</t>
+          <t>Sadiq</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>07033162971</t>
+          <t>07035983882</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3461,33 +3473,37 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>std125</t>
+          <t>std145</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Haliru</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ismat</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Sadiq</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Akubursa</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>08032892838</t>
+          <t>08060671508</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3499,23 +3515,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>std126</t>
+          <t>std146</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Idris</t>
+          <t>Bawa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nabeela</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Bilikisu</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Abubakar</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>08009997778</t>
+          <t>08065554954</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3525,7 +3545,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3537,27 +3557,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>std127</t>
+          <t>std147</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rabiu</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Idris</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Al-Mustapha</t>
-        </is>
-      </c>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>07032297722</t>
+          <t>08123584340</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3567,7 +3583,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3579,33 +3595,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>std128</t>
+          <t>std148</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alhassan</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ashiru</t>
+          <t>Idris</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>08165650509</t>
+          <t>08100999778</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>JSS2B</t>
+          <t>JSS2C</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3617,27 +3633,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>std129</t>
+          <t>std149</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Yakubu</t>
+          <t>Abdallah</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nabeela</t>
+          <t>Hasina</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Limar</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>08163234854</t>
+          <t>08034423215</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3659,32 +3675,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>std130</t>
+          <t>std150</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Abbas</t>
+          <t>Abdullahi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Zainab</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sani</t>
+          <t>Wonukai</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>08032894993</t>
+          <t>08065359057</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3701,27 +3717,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>std131</t>
+          <t>std151</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Danjuma</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rahma</t>
+          <t>Halima</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ene</t>
+          <t>Arfo</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>08033752523</t>
+          <t>08069661006</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3743,32 +3759,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>std132</t>
+          <t>std152</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Abdulganiyu</t>
+          <t>Rabiu</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Muritala</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>D.</t>
+          <t>Ojali</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>08031526007</t>
+          <t>07031591970</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3785,27 +3801,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>std133</t>
+          <t>std153</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Balarabe</t>
+          <t>Babagida</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Zainab</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Yusuf</t>
+          <t>Bello</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>07044322222</t>
+          <t>07032901805</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3827,32 +3843,28 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>std134</t>
+          <t>std154</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hamza</t>
+          <t>Bashir</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sani</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Omolori</t>
-        </is>
-      </c>
+          <t>Hanifa</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>08033821780</t>
+          <t>08069205599</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3869,28 +3881,28 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>std135</t>
+          <t>std155</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lukman</t>
+          <t>Abdulladir</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Maryam</t>
+          <t>Mushibahu</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>08133393282</t>
+          <t>08065895999</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3907,27 +3919,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>std136</t>
+          <t>std156</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rabiu</t>
+          <t>Aminu</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Maryam</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Alhassan</t>
+          <t>Dahiru</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>07030453600</t>
+          <t>080377885??</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3949,20 +3961,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>std137</t>
+          <t>std157</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hussein</t>
+          <t>Ishaq</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Mukhtar</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Aliyu</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lolo</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>07035352050</t>
@@ -3987,32 +4003,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>std138</t>
+          <t>std158</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Abubakar</t>
+          <t>Mustapha</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Aisha</t>
+          <t>Onuche</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Imran</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>08033166893</t>
+          <t>08067871919</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -4029,27 +4045,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>std139</t>
+          <t>std159</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Muhammad</t>
+          <t>Ashiru</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ilyasu</t>
+          <t>Al-Hussein</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Mu'id</t>
+          <t>I.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>08062198188</t>
+          <t>08165650569</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4068,824 +4084,8 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>std140</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Usman</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Hafsat</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Mari</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>08026033049</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>std141</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Sabo</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>08036880438</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>std142</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>080358681604?</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>std143</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Muhammad</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Haliru</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>08032332868</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>std144</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Abubakar</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Farida</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Sadiq</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>07035983882</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>std145</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Haliru</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Sadiq</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Akubursa</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>08060671508</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>std146</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Bawa</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Bilikisu</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Abubakar</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>08065554954</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>std147</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Adam</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>08123584340</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>std148</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Idris</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>08100999778</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>std149</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Abdallah</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Hasina</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>08034423215</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>std150</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Abdullahi</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Wonukai</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>08065359057</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>std151</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Mustapha</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Halima</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Arfo</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>08069661006</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>std152</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Rabiu</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Jasmine</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Ojali</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>07031591970</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>std153</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Babagida</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Zainab</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Bello</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>07032901805</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>std154</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Bashir</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Hanifa</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>08069205599</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>std155</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Abdulladir</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Mushibahu</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>08065895999</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>std156</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Aminu</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Maryam</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Dahiru</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>080377885??</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>std157</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Ishaq</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Aliyu</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Lolo</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>07035352050</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>std158</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Mustapha</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Onuche</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>08067871919</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>std159</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Ashiru</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Al-Hussein</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>I.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>08165650569</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>JSS2C</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>JSS2</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H110"/>
+  <autoFilter ref="A1:H90"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>